--- a/data/Janthiniformis EAG/depolarizations.xlsx
+++ b/data/Janthiniformis EAG/depolarizations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://montanaedu-my.sharepoint.com/personal/n47c392_msu_montana_edu/Documents/MSU PhD/Projects/Janthiniformis EAG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksonstrand/Documents/GitHub/toadflax_hybrids_2026/data/Janthiniformis EAG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1050" documentId="8_{422E7F73-66A7-434E-825F-26FEFC6B9428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D71B5766-94BE-A146-A699-F9051843508A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC2ACC2-9985-474A-9A37-B30FD403E87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19660" activeTab="1" xr2:uid="{C2DF0F49-E774-604A-A874-C69BEAC46AA2}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{C2DF0F49-E774-604A-A874-C69BEAC46AA2}"/>
   </bookViews>
   <sheets>
     <sheet name="compound response" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="41">
   <si>
     <t>species</t>
   </si>
@@ -4588,52 +4588,7 @@
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>23</v>
-      </c>
-      <c r="B92" t="s">
-        <v>23</v>
-      </c>
-      <c r="C92" t="s">
-        <v>23</v>
-      </c>
-      <c r="D92" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="E92" s="3">
-        <f t="shared" ref="E92" ca="1" si="6">AVERAGE(I92:M92)</f>
-        <v>2.024</v>
-      </c>
-      <c r="F92" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G92" s="3">
-        <f t="shared" ref="G92" ca="1" si="7">ROUND(STDEV(I92:M92)/SQRT(COUNT(I92:M92)),2)</f>
-        <v>0.24</v>
-      </c>
-      <c r="H92" s="2">
-        <v>5</v>
-      </c>
-      <c r="I92" s="4">
-        <f ca="1">ABS(ROUND($D92 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($F92*SQRT($H92))),2))</f>
-        <v>2.1</v>
-      </c>
-      <c r="J92" s="2">
-        <f ca="1">ABS(ROUND($D92 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($F92*SQRT($H92))),2))</f>
-        <v>1.62</v>
-      </c>
-      <c r="K92" s="2">
-        <f ca="1">ABS(ROUND($D92 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($F92*SQRT($H92))),2))</f>
-        <v>2.34</v>
-      </c>
-      <c r="L92" s="2">
-        <f ca="1">ABS(ROUND($D92 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($F92*SQRT($H92))),2))</f>
-        <v>2.7</v>
-      </c>
-      <c r="M92" s="5">
-        <f ca="1">ABS(ROUND($D92 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($F92*SQRT($H92))),2))</f>
-        <v>1.36</v>
-      </c>
+      <c r="E92" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -6538,34 +6493,34 @@
       </c>
       <c r="F34" s="4">
         <f ca="1">ROUND(AVERAGE(I34:M34),2)</f>
-        <v>12.02</v>
+        <v>8.57</v>
       </c>
       <c r="G34" s="2">
         <f ca="1">ROUND(STDEV(I34:M34)/SQRT(COUNT(I34:M34)),2)</f>
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="H34" s="2">
         <v>5</v>
       </c>
       <c r="I34" s="4">
         <f ca="1">ABS(ROUND($D34 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($E34*SQRT($H34))),2))</f>
-        <v>21.07</v>
+        <v>18.64</v>
       </c>
       <c r="J34" s="2">
         <f ca="1">ABS(ROUND($D34 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($E34*SQRT($H34))),2))</f>
-        <v>11.86</v>
+        <v>6.68</v>
       </c>
       <c r="K34" s="2">
         <f ca="1">ABS(ROUND($D34 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($E34*SQRT($H34))),2))</f>
-        <v>5.15</v>
+        <v>6.38</v>
       </c>
       <c r="L34" s="2">
         <f ca="1">ABS(ROUND($D34 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($E34*SQRT($H34))),2))</f>
-        <v>6.78</v>
+        <v>8.11</v>
       </c>
       <c r="M34" s="2">
         <f ca="1">ABS(ROUND($D34 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($E34*SQRT($H34))),2))</f>
-        <v>15.23</v>
+        <v>3.06</v>
       </c>
     </row>
   </sheetData>
@@ -6591,7 +6546,7 @@
       </c>
       <c r="B1">
         <f ca="1">ROUND($A$1 + (_xlfn.NORM.INV(RAND(), 0, 1) * $A$4),2)</f>
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -6600,7 +6555,7 @@
       </c>
       <c r="B2">
         <f t="shared" ref="B2:B5" ca="1" si="0">ROUND($A$1 + (_xlfn.NORM.INV(RAND(), 0, 1) * $A$4),2)</f>
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -6615,15 +6570,15 @@
       </c>
       <c r="B3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.56</v>
+        <v>1.17</v>
       </c>
       <c r="D3">
         <f ca="1">AVERAGE(B1:B5)</f>
-        <v>1.1539999999999999</v>
+        <v>1.1779999999999999</v>
       </c>
       <c r="E3">
         <f ca="1">STDEV(B1:B5)/SQRT(A3)</f>
-        <v>0.14582866659199795</v>
+        <v>4.7265209192385894E-2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -6633,13 +6588,13 @@
       </c>
       <c r="B4">
         <f t="shared" ca="1" si="0"/>
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5">
         <f t="shared" ca="1" si="0"/>
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>
